--- a/docs/build/lakeshore-enterprise-context/source/07_data_analytics_reporting/data_products.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/07_data_analytics_reporting/data_products.xlsx
@@ -484,12 +484,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
@@ -506,12 +506,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Build</t>
         </is>
       </c>
     </row>
@@ -550,12 +550,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Build</t>
         </is>
       </c>
     </row>
